--- a/extenbooks/S504.xlsx
+++ b/extenbooks/S504.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA NIPA + BLS CES, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S504-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S504-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S504-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>88.41</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>85.02</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>93.16</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>105.91</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>105.91</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>111.01</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>111.01</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>117.39</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>117.39</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>111.95</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>120.52</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>120.52</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>128.82</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>127.72</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>127.72</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>139.57</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>139.57</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>144.23</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>144.23</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>146.13</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>146.13</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>155.54</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>155.54</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>162.76</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>172</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>188.43</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>188.43</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>207.07</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>207.07</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>216.26</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>216.26</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>236.77</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>236.77</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>261.22</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>261.22</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>270.43</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>270.43</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>287.53</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>324.3</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>370.49</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>398.5</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>410.75</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>410.75</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>459.63</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>459.63</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>515.8099999999999</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>515.8099999999999</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>589.2</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>589.2</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>664.78</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>664.78</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>706.53</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>706.53</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>772.35</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>772.35</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>786.53</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>786.53</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>839.73</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>839.73</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>928.6799999999999</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>928.6799999999999</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>967.99</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>967.99</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>998.55</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>998.55</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>1060.9</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>1060.9</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>1146.22</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>1146.22</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,390 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>1206.4</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1206.4</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1620.228590999999</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1620.228590999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1710.010597408279</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1710.010597408279</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1822.622319191707</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1822.622319191707</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1814.176143367777</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1814.176143367777</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1769.627520622427</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1769.627520622427</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1783.678767180713</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1783.678767180713</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1866.781684431051</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1866.781684431051</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1946.259047776357</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1946.259047776357</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2048.399980000346</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2048.399980000346</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2125.120498265002</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2125.120498265002</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2119.869082215981</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2119.869082215981</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1901.079068344436</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1901.079068344436</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1895.840706662993</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1895.840706662993</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1974.902703767134</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1974.902703767134</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2072.316768166659</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2072.316768166659</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2133.789785098472</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2133.789785098472</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2252.023192265903</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2252.023192265903</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2351.724144513216</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2351.724144513216</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2393.098182415373</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2393.098182415373</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>2510.225528620615</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2510.225528620615</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2655.162238052236</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2655.162238052236</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2778.973420458175</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2778.973420458175</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2749.059930530121</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2749.059930530121</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2928.411513183341</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2928.411513183341</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>3171.753232189837</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>3171.753232189837</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>3350.040290504985</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>3350.040290504985</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>3531.925607229316</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3531.925607229316</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_4, Fig_6_1, Fig_6_2, Fig_6_3, Fig_9_1</t>
+          <t>Fig_5_4, Fig_6_1, Fig_6_2, Fig_6_3, Fig_9_1, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,386 +1642,391 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S504-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S504-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA NIPA + BLS CES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S504-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S504 — Variable Capital (V*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t># S504 — Variable Capital (V*)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S504-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S504-EXT` | BEA NIPA + BLS CES | 1990-2024 | billions_dollars |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>| `S504-COMBINED` |  | 1948-2024 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>| `S504-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S504-EXT` | BEA NIPA + BLS CES | 1990-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>| `S504-COMBINED` |  | 1948-2024 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>### S504-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2. Extract column `V_star` (and the `year` index).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>### S504-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `V_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S504.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2034,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -1385,65 +2042,105 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S504.csv</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1460,10 +2157,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1488,245 +2185,307 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V* = W × (V*/W), where W is total employee compensation and V*/W is the productive wage share. The productive wage share approximation V*/W ≈ Lp/L holds because the ratio of unproductive to productive employee compensation per worker (ec_u/ec_p) is approximately 1 (p.113). More precisely, V* = w_p × x × L_p where w_p is the productive wage rate and x is hours per worker.</t>
+          <t>(wp)j = unit wage of production workers in the jth production sector, j = 1,..., k (from BLS), except services, for which (wp)serv = ecserv; xj ≡ (EC/WS)j = ratio of employee compensation EC to wages and salaries W, in the jth production sector, j = 1,..., k (from NIPA); (ecp)j = (wp)j·(xj) = estimated employee compensation of production workers in the jth production sector; Vj ≡ ecj · (Lp)j ≡ (Wp)j = variable capital in the jth production sector; V* ≡ Wp = Σ(Wp)j = total variable capital; Wu ≡ W − V* = total wages of unproductive workers in all sectors; ecp ≡ Wp/Lp = average wage of productive workers; ecu ≡ Wu/Lu = average wage of unproductive workers.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 p.113; Knowledge_Base/equations/page_340_equations.txt</t>
+          <t>ST_1994, Ch5, p.113; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Subseries A (1948-1989): from book Table 5.5. Extension S504-EXT derives V* = W × (V*/W) using BEA NIPA Table 1.12 for total compensation (W) and BLS CES production worker share for V*/W proxy. Spliced at 1989 to form S504-COMBINED. Depends on S512 for the productive wage share.</t>
+          <t>Figure 5.8 contrasts the levels of real variable capital and of the total real wage bill. Their absolute growth is greater than that of the corresponding labor totals in Figure 5.7 because the wage measures also incorporate the effects of growing real wages. But the relative movements of wage and employment measures is virtually the same, as is evident in Figure 5.9. V*/W declines by 34%, while Lp/L declines by 37%.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv; BEA NIPA 1.12; BLS CES</t>
+          <t>ST_1994, Ch5, p.113; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.4 shows V* as the wage component within GFP. Figs 6.1-6.3 use V* in wage-share and distribution analysis. Fig 9.1 uses V* in long-run accumulation dynamics.</t>
+          <t>Productive labor is the production labor employed in capitalist production sectors: agriculture, mining, construction, transportation and public utilities, manufacturing, and productive services (defined as all services except business services, legal services, and private households, as in Table E.1).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.4, 6.1-6.3, 9.1</t>
+          <t>ST_1994, Ch5, p.108-109; chunk_13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Book benchmark values from Table 5.5: 1948, 1958, 1967, 1977, 1989. The extension should match the 1989 book value at the splice point. V* grows slower than W over time as productive labor share declines.</t>
+          <t>The theoretical difference between Marxian and orthodox economic analysis is reflected in a fundamentally different empirical picture of capitalist reality.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.5</t>
+          <t>ST_1994, Ch5, p.140; extracted_content/text/page_140_productivity_analysis.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2013) computes variable capital using BLS industry codes with a different sector classification. Key difference: Mohun classifies Information sector as entirely productive and retail eating/drinking as productive, yielding a higher V*. Mohun's data available in mohun_variable_capital*.csv and mohun_exploitation_rates*.csv.</t>
+          <t>V_j ≡ ec_j · (Lp)_j ≡ (Wp)_j = variable capital in the jth production sector; V* ≡ Wp = ∑ (Wp)_j = total variable capital; Wu ≡ W − V* = total wages of unproductive workers in all sectors.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The ec_u/ec_p ≈ 1 approximation may deteriorate over time as wage inequality between productive and unproductive sectors diverges. Post-1989 extension quality depends on this approximation holding.</t>
+          <t>(ecp)_j = (wp)_j · (x_j) = estimated employee compensation of production workers in the jth production sector, where (wp)_j is the unit wage of production workers in the jth production sector from BLS and x_j = (EC/WS)_j is the ratio of employee compensation to wages and salaries from NIPA.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, p.113; CHAPTER_5_INVESTIGATION.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-007 (SIC-NAICS Gap Interpolation, 2026-04-08): Log-linear interpolation is used for the ec_u/ec_p ratio over 1990-1997, bridging from the 1989 book endpoint to the first NAICS-era BEA NIPA 6.2D value (1998). S504 is directly affected: the V*/W proxy used in the extension period relies on this interpolated ec_u/ec_p ratio. Confirmed max deviation from constant assumption = 0.42. Values for 1990-1997 carry interpolated classification weights and are documented under ADJ-002.</t>
+          <t>V*/W declines by 34%, while Lp/L declines by 37%. The unit wages of productive and unproductive workers change only slightly, whereas their relative employments change drastically. We can therefore unambiguously conclude that the relative decline in productive to total wages Wp/W (= V*/W) is almost entirely due to the relative decline in productive to total employment Lp/L.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-007</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-009 (S504 Splice Fix Deferred — Unit Scaling Issue, 2026-04-09): The S504 splice quality is documented at CR=0.81 (WARN-04, accepted). An attempted fix using NIPA T20100 aggregate compensation worsened the splice to CR=0.11 due to a unit scaling mismatch: book-period V* (millions, from Table 5.7 ec_p × L_p pathway) differs in base unit from extension-period W × (V*/W) (derived from BEA 6.2D). The correct fix requires a comprehensive Wave 2 unit normalization. In the meantime, `Inputs/API_Data/BEA/nipa_T20100_compensation_1929_2025.csv` has been fetched and is available for that future work. The CR=0.81 splice is the accepted current state.</t>
+          <t>V* = W × (V*/W), where W is total employee compensation and V*/W is the productive wage share. The productive wage share approximation V*/W ≈ Lp/L holds because the ratio of unproductive to productive employee compensation per worker (ec_u/ec_p) is approximately 1 (p.113). More precisely, V* = w_p × x × L_p where w_p is the productive wage rate and x is hours per worker.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>ST_1994, Ch5 p.113; Knowledge_Base/equations/page_340_equations.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Subseries A (1948-1989): from book Table 5.5. Extension S504-EXT derives V* = W × (V*/W) using BEA NIPA Table 1.12 for total compensation (W) and BLS CES production worker share for V*/W proxy. Spliced at 1989 to form S504-COMBINED. Depends on S512 for the productive wage share.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv; BEA NIPA 1.12; BLS CES</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>figure_context</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Variable capital measures the wages of productive workers: V* = W × (Lp/L). Book data (1948-1989) extended via BEA compensation × BLS production worker share, spliced at 1989. Depends on S512.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Fig 5.4 shows V* as the wage component within GFP. Figs 6.1-6.3 use V* in wage-share and distribution analysis. Fig 9.1 uses V* in long-run accumulation dynamics.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.4, 6.1-6.3, 9.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>benchmark_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Book benchmark values from Table 5.5: 1948, 1958, 1967, 1977, 1989. The extension should match the 1989 book value at the splice point. V* grows slower than W over time as productive labor share declines.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.5</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>external_comparison</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mohun (2013) computes variable capital using BLS industry codes with a different sector classification. Key difference: Mohun classifies Information sector as entirely productive and retail eating/drinking as productive, yielding a higher V*. Mohun's data available in mohun_variable_capital*.csv and mohun_exploitation_rates*.csv.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ec_u/ec_p ≈ 1 approximation may weaken post-1989</t>
+          <t>The ec_u/ec_p ≈ 1 approximation may deteriorate over time as wage inequality between productive and unproductive sectors diverges. Post-1989 extension quality depends on this approximation holding.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, p.113; CHAPTER_5_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Extension depends on S512 productive wage share quality</t>
+          <t>[internal-decision-record] (SIC-NAICS Gap Interpolation, 2026-04-08): Log-linear interpolation is used for the ec_u/ec_p ratio over 1990-1997, bridging from the 1989 book endpoint to the first NAICS-era BEA NIPA 6.2D value (1998). S504 is directly affected: the V*/W proxy used in the extension period relies on this interpolated ec_u/ec_p ratio. Confirmed max deviation from constant assumption = 0.42. Values for 1990-1997 carry interpolated classification weights and are documented under ADJ-002.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohun classification yields systematically higher V*</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Splice quality CR=0.81 (WARN-04, accepted) — unit mismatch blocks improvement until Wave 2 normalization (DEC-009)</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] (S504 Splice Fix Deferred — Unit Scaling Issue, 2026-04-09): The S504 splice quality is documented at CR=0.81 (WARN-04, accepted). An attempted fix using NIPA T20100 aggregate compensation worsened the splice to CR=0.11 due to a unit scaling mismatch: book-period V* (millions, from Table 5.7 ec_p × L_p pathway) differs in base unit from extension-period W × (V*/W) (derived from BEA 6.2D). The correct fix requires a comprehensive Wave 2 unit normalization. In the meantime, `Inputs/API_Data/BEA/nipa_T20100_compensation_1929_2025.csv` has been fetched and is available for that future work. The CR=0.81 splice is the accepted current state.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1990-1997 ec_u/ec_p interpolated via log-linear method (DEC-007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>113</v>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S503</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>S505</t>
-        </is>
-      </c>
-    </row>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S506</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>S510</t>
-        </is>
-      </c>
-    </row>
+          <t>Variable capital measures the wages of productive workers: V* = W × (Lp/L). Book data (1948-1989) extended via BEA compensation × BLS production worker share, spliced at 1989. Depends on S512.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>S512</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1734,37 +2493,125 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
+          <t>ec_u/ec_p ≈ 1 approximation may weaken post-1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Extension depends on S512 productive wage share quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mohun classification yields systematically higher V*</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Splice quality CR=0.81 (WARN-04, accepted) — unit mismatch blocks improvement until Wave 2 normalization ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1990-1997 ec_u/ec_p interpolated via log-linear method ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S503</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S505</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S510</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S512</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>S515</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1781,14 +2628,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1856,7 +2703,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>V* = W Ã— (V*/W)</t>
+          <t>V* = W — (V*/W)</t>
         </is>
       </c>
     </row>
@@ -1885,91 +2732,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S512']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S504-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S504-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Appendix H.1 column V_star (productive variable capital, 1948-1989); Chapter 5 pp. 161-180 (decomposition of V into productive and unproductive wages)", "shaikh_appendix_ref": "Appendix H.1 (V_star, 1948-1989); Table 5.7 (productive labor and wage shares); Figure 5.6 (aggregate measures)", "extension_source": "BEA NIPA Table 6.2 (compensation of employees, by industry) + BLS CES (production-worker wages, by industry), filtered through the productive/unproductive labor classification (depends on S512 productive wage share)", "extension_url": "https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2 (NIPA); https://www.bls.gov/ces/ (CES)", "conceptual_continuity": "Variable Capital V* is wages paid to productive workers (production workers in productive industries). The construct is observable from BEA compensation data combined with BLS production-worker classification, but only after applying the productive/unproductive partition. The extension is computed via a derive method that leans on S512 (productive wage share) being extended first.", "vintage_note": "BEA NIPA compensation tables have undergone comprehensive revisions (1999, 2003, 2013); BLS CES underwent the 2003 establishment-survey overhaul. The productive/unproductive partition (Appendix C) must be updated for NAICS industries. Treatment of stock-based and deferred compensation differs between vintages.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S512"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 88.41, "1972": 324.3, "1989": 1206.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0, 15000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S504.xlsx
+++ b/extenbooks/S504.xlsx
@@ -447,13 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
           <t>BEA NIPA + BLS CES, units=billions_usd</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>derived, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -497,6 +503,11 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S504-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S504-INTERP</t>
         </is>
       </c>
     </row>
@@ -513,18 +524,24 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
+      <c r="E3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>85.02</v>
+        <v>85.021</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>85.02</v>
+        <v>85.021</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -533,12 +550,15 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>93.16</v>
+        <v>93.161</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>93.16</v>
+        <v>93.161</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -547,12 +567,15 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>105.91</v>
+        <v>105.912</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>105.91</v>
+        <v>105.912</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -561,12 +584,15 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>111.01</v>
+        <v>111.013</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>111.01</v>
+        <v>111.013</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -575,12 +601,15 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>117.39</v>
+        <v>117.388</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>117.39</v>
+        <v>117.388</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -589,12 +618,15 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>111.95</v>
+        <v>111.952</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>111.95</v>
+        <v>111.952</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -603,12 +635,15 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>120.52</v>
+        <v>120.518</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>120.52</v>
+        <v>120.518</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -617,12 +652,15 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>128.82</v>
+        <v>128.824</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>128.82</v>
+        <v>128.824</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E11" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -631,12 +669,15 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>133</v>
+        <v>132.999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>133</v>
+        <v>132.999</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E12" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -645,12 +686,15 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>127.72</v>
+        <v>127.717</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>127.72</v>
+        <v>127.717</v>
       </c>
       <c r="D13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -667,6 +711,9 @@
       <c r="D14" s="3" t="n">
         <v/>
       </c>
+      <c r="E14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -681,6 +728,9 @@
       <c r="D15" s="3" t="n">
         <v/>
       </c>
+      <c r="E15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -695,18 +745,24 @@
       <c r="D16" s="3" t="n">
         <v/>
       </c>
+      <c r="E16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>155.54</v>
+        <v>155.536</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>155.54</v>
+        <v>155.536</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -715,12 +771,15 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>162.76</v>
+        <v>162.758</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>162.76</v>
+        <v>162.758</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -729,12 +788,15 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>172</v>
+        <v>171.998</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>172</v>
+        <v>171.998</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -743,12 +805,15 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>188.43</v>
+        <v>188.426</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>188.43</v>
+        <v>188.426</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -757,12 +822,15 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>207.07</v>
+        <v>207.068</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>207.07</v>
+        <v>207.068</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -771,12 +839,15 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>216.26</v>
+        <v>216.257</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>216.26</v>
+        <v>216.257</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E22" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -785,12 +856,15 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>236.77</v>
+        <v>236.769</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>236.77</v>
+        <v>236.769</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -799,12 +873,15 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>261.22</v>
+        <v>261.216</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>261.22</v>
+        <v>261.216</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -813,12 +890,15 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>270.43</v>
+        <v>270.432</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>270.43</v>
+        <v>270.432</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -827,12 +907,15 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>287.53</v>
+        <v>287.525</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>287.53</v>
+        <v>287.525</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E26" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -841,12 +924,15 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>324.3</v>
+        <v>324.303</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>324.3</v>
+        <v>324.303</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E27" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -863,18 +949,24 @@
       <c r="D28" s="3" t="n">
         <v/>
       </c>
+      <c r="E28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>398.5</v>
+        <v>398.505</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>398.5</v>
+        <v>398.505</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -891,18 +983,24 @@
       <c r="D30" s="3" t="n">
         <v/>
       </c>
+      <c r="E30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>459.63</v>
+        <v>459.625</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>459.63</v>
+        <v>459.625</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -911,12 +1009,15 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>515.8099999999999</v>
+        <v>515.814</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>515.8099999999999</v>
+        <v>515.814</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E32" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -925,12 +1026,15 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>589.2</v>
+        <v>589.202</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>589.2</v>
+        <v>589.202</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E33" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -939,12 +1043,15 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>664.78</v>
+        <v>664.783</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>664.78</v>
+        <v>664.783</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E34" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -953,12 +1060,15 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>706.53</v>
+        <v>706.526</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>706.53</v>
+        <v>706.526</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E35" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -967,12 +1077,15 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>772.35</v>
+        <v>772.351</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>772.35</v>
+        <v>772.351</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -981,12 +1094,15 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>786.53</v>
+        <v>786.528</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>786.53</v>
+        <v>786.528</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -995,12 +1111,15 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>839.73</v>
+        <v>839.732</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>839.73</v>
+        <v>839.732</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1017,18 +1136,24 @@
       <c r="D39" s="3" t="n">
         <v/>
       </c>
+      <c r="E39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>967.99</v>
+        <v>967.9930000000001</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>967.99</v>
+        <v>967.9930000000001</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1037,12 +1162,15 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>998.55</v>
+        <v>998.546</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>998.55</v>
+        <v>998.546</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E41" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1051,12 +1179,15 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1060.9</v>
+        <v>1060.901</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1060.9</v>
+        <v>1060.901</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1065,12 +1196,15 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1146.22</v>
+        <v>1146.222</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1146.22</v>
+        <v>1146.222</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1079,391 +1213,611 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1206.4</v>
+        <v>1206.396</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1206.4</v>
+        <v>1206.396</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1620.228590999999</v>
+        <v>1244.621309450054</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1620.228590999999</v>
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1244.621309450054</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1710.010597408279</v>
+        <v>1284.057808495028</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1710.010597408279</v>
+        <v/>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1284.057808495028</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1822.622319191707</v>
+        <v>1324.743874332017</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1822.622319191707</v>
+        <v/>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1324.743874332017</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1814.176143367777</v>
+        <v>1366.719100160356</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1814.176143367777</v>
+        <v/>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1366.719100160356</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1769.627520622427</v>
+        <v>1410.024333711304</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1769.627520622427</v>
+        <v/>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1410.024333711304</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1783.678767180713</v>
+        <v>1454.701716998567</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1783.678767180713</v>
+        <v/>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1454.701716998567</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1866.781684431051</v>
+        <v>1500.794727328338</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1866.781684431051</v>
+        <v/>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1500.794727328338</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1946.259047776357</v>
+        <v>1548.348219608763</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1946.259047776357</v>
+        <v/>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1548.348219608763</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2048.399980000346</v>
+        <v>1597.408469999999</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2048.399980000346</v>
+        <v>1597.408469999999</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2125.120498265002</v>
+        <v>1685.925941106754</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2125.120498265002</v>
+        <v>1685.925941106754</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2119.869082215981</v>
+        <v>1796.951582301683</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2119.869082215981</v>
+        <v>1796.951582301683</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1901.079068344436</v>
+        <v>1788.624366700626</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1901.079068344436</v>
+        <v>1788.624366700626</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1895.840706662993</v>
+        <v>1744.703189346055</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1895.840706662993</v>
+        <v>1744.703189346055</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1974.902703767134</v>
+        <v>1758.556531023239</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1974.902703767134</v>
+        <v>1758.556531023239</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2072.316768166659</v>
+        <v>1840.488984650332</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2072.316768166659</v>
+        <v>1840.488984650332</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>2133.789785098472</v>
+        <v>1918.846948511902</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2133.789785098472</v>
+        <v>1918.846948511902</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2252.023192265903</v>
+        <v>2019.549276056679</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>2252.023192265903</v>
+        <v>2019.549276056679</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2351.724144513216</v>
+        <v>2095.189223641552</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2351.724144513216</v>
+        <v>2095.189223641552</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>2393.098182415373</v>
+        <v>2090.011771198855</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2393.098182415373</v>
+        <v>2090.011771198855</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>2510.225528620615</v>
+        <v>1874.303306818457</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2510.225528620615</v>
+        <v>1874.303306818457</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>2655.162238052236</v>
+        <v>1869.138724879007</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2655.162238052236</v>
+        <v>1869.138724879007</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2778.973420458175</v>
+        <v>1947.08717272816</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2778.973420458175</v>
+        <v>1947.08717272816</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2749.059930530121</v>
+        <v>2043.129208051635</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2749.059930530121</v>
+        <v>2043.129208051635</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2928.411513183341</v>
+        <v>2103.736407843564</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2928.411513183341</v>
+        <v>2103.736407843564</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>3171.753232189837</v>
+        <v>2220.304555755116</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>3171.753232189837</v>
+        <v>2220.304555755116</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>3350.040290504985</v>
+        <v>2318.601269238382</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>3350.040290504985</v>
+        <v>2318.601269238382</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>2359.39257421234</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2359.39257421234</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>2474.870239485114</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2474.870239485114</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>2617.765586812063</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2617.765586812063</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>2739.832949747497</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>2739.832949747497</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2710.340776578992</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2710.340776578992</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2887.166280603295</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>2887.166280603295</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>3127.08065145477</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3127.08065145477</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>3302.856624441536</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>3302.856624441536</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>3531.925607229316</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>3531.925607229316</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3482.18017614158</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>3482.18017614158</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1685,40 +2039,44 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S504-INTERP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S504 — Variable Capital (V*)</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S504 — Variable Capital (V*)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix H.1</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
@@ -1726,7 +2084,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Units**: billions_usd</t>
+          <t>**Source Table**: Appendix H.1</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2092,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2100,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
         </is>
       </c>
     </row>
@@ -1750,87 +2108,87 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>## Subseries</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
@@ -1838,7 +2196,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>| `S504-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2204,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>| `S504-EXT` | BEA NIPA + BLS CES | 1990-2024 | billions_dollars |</t>
+          <t>| `S504-A` | S&amp;T 1994 Appendix H.1 | 1948-1989 | billions_dollars |</t>
         </is>
       </c>
     </row>
@@ -1854,19 +2212,23 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>| `S504-COMBINED` |  | 1948-2024 | billions_dollars |</t>
+          <t>| `S504-EXT` | BEA NIPA + BLS CES (derived V* = (V*/W)·W) | 1998-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>| `S504-INTERP` | Log-linear interp between S504-A(1989) and S504-EXT(1998) | 1990-1997 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| `S504-COMBINED` | S504-A ∪ S504-INTERP ∪ S504-EXT | 1948-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
@@ -1878,7 +2240,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2252,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>### S504-A (book period, 1948-1989)</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1902,35 +2264,35 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+          <t>### S504-A (book period, 1948-1989)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2. Extract column `V_star` (and the `year` index).</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2. Extract column `V_star` (and the `year` index).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+          <t>3. No further transformation — this is the canonical published value.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2304,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +2316,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>### S504-INTERP (1990-1997 bridge)</t>
         </is>
       </c>
     </row>
@@ -1966,67 +2328,79 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
+          <t>**1990-1997 bridge**: log-linear interpolation between the book 1989 endpoint</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(`S504-A[1989]` = 1206.40 $B) and the BEA-derived first-EXT value</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+          <t>(`S504-EXT[1998]` = 1620.23 $B), consistent with the S501–S503 bridge per</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>`Technical/Build/BUILD_NARRATIVE.md` Stage 5 cohort 3.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Formula: `v(t) = exp( ln(v0) + (t - 1989)/(1998 - 1989) · (ln(v1) - ln(v0)) )`</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>These eight values are **INTERPOLATED estimates**, not published BEA data.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Documentation script: `code/M04_manual/M04_S504_1990_1997_bridge.py`</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(also acts as a verifier — re-derives values from endpoints and asserts</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>equality with the on-disk S504-INTERP rows). Sample values: 1991 = 1288.12,</t>
         </is>
       </c>
     </row>
@@ -2034,39 +2408,31 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>1995 = 1468.52.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
+          <t>### S504-EXT (1998-2024)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S504.csv</t>
+          <t>Derived V* = (V*/W) · W where V*/W comes from `S504-EXT` (S512 must run</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2440,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
+          <t>first) and W is BEA NIPA T20100 total compensation. Begins 1998 because</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2448,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>BEA NIPA 6.2D (compensation by industry, NAICS) begins 1998.</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2460,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>### S504-COMBINED</t>
         </is>
       </c>
     </row>
@@ -2106,41 +2472,225 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t>Concatenation: 1948-1989 from S504-A, 1990-1997 from S504-INTERP (bridge),</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1998-2024 from S504-EXT.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>## Provenance Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S504.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -2326,7 +2876,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subseries A (1948-1989): from book Table 5.5. Extension S504-EXT derives V* = W × (V*/W) using BEA NIPA Table 1.12 for total compensation (W) and BLS CES production worker share for V*/W proxy. Spliced at 1989 to form S504-COMBINED. Depends on S512 for the productive wage share.</t>
+          <t>Subseries A (1948-1989): from book Table 5.6 ('Total wages and variable capital, 1948-89', p.115; corrected 2026-06-11 from the erroneous 'Table 5.5', which is 'Total wages and productive employment'). Extension S504-EXT derives V* = W × (V*/W) using BEA NIPA Table 1.12 for total compensation (W) and BLS CES production worker share for V*/W proxy. Spliced at 1989 to form S504-COMBINED. Depends on S512 for the productive wage share.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2360,12 +2910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Book benchmark values from Table 5.5: 1948, 1958, 1967, 1977, 1989. The extension should match the 1989 book value at the splice point. V* grows slower than W over time as productive labor share declines.</t>
+          <t>Book benchmark values from Table 5.6: 1948, 1958, 1967, 1977, 1989. The extension should match the 1989 book value at the splice point. V* grows slower than W over time as productive labor share declines.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.5</t>
+          <t>ST_1994, Table 5.6</t>
         </is>
       </c>
     </row>
@@ -2628,10 +3178,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2907,6 +3457,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S504.xlsx
+++ b/extenbooks/S504.xlsx
@@ -447,14 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,11 +477,6 @@
           <t>BEA NIPA + BLS CES, units=billions_usd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>derived, units=billions_usd</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -503,11 +497,6 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S504-EXT</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>S504-INTERP</t>
         </is>
       </c>
     </row>
@@ -524,9 +513,6 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
-      <c r="E3" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -541,9 +527,6 @@
       <c r="D4" s="3" t="n">
         <v/>
       </c>
-      <c r="E4" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -558,9 +541,6 @@
       <c r="D5" s="3" t="n">
         <v/>
       </c>
-      <c r="E5" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -575,9 +555,6 @@
       <c r="D6" s="3" t="n">
         <v/>
       </c>
-      <c r="E6" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -592,9 +569,6 @@
       <c r="D7" s="3" t="n">
         <v/>
       </c>
-      <c r="E7" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -609,9 +583,6 @@
       <c r="D8" s="3" t="n">
         <v/>
       </c>
-      <c r="E8" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -626,9 +597,6 @@
       <c r="D9" s="3" t="n">
         <v/>
       </c>
-      <c r="E9" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -643,9 +611,6 @@
       <c r="D10" s="3" t="n">
         <v/>
       </c>
-      <c r="E10" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -660,9 +625,6 @@
       <c r="D11" s="3" t="n">
         <v/>
       </c>
-      <c r="E11" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -677,9 +639,6 @@
       <c r="D12" s="3" t="n">
         <v/>
       </c>
-      <c r="E12" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -694,9 +653,6 @@
       <c r="D13" s="3" t="n">
         <v/>
       </c>
-      <c r="E13" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -711,9 +667,6 @@
       <c r="D14" s="3" t="n">
         <v/>
       </c>
-      <c r="E14" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -728,9 +681,6 @@
       <c r="D15" s="3" t="n">
         <v/>
       </c>
-      <c r="E15" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -745,9 +695,6 @@
       <c r="D16" s="3" t="n">
         <v/>
       </c>
-      <c r="E16" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -762,9 +709,6 @@
       <c r="D17" s="3" t="n">
         <v/>
       </c>
-      <c r="E17" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -779,9 +723,6 @@
       <c r="D18" s="3" t="n">
         <v/>
       </c>
-      <c r="E18" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -796,9 +737,6 @@
       <c r="D19" s="3" t="n">
         <v/>
       </c>
-      <c r="E19" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -813,9 +751,6 @@
       <c r="D20" s="3" t="n">
         <v/>
       </c>
-      <c r="E20" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -830,9 +765,6 @@
       <c r="D21" s="3" t="n">
         <v/>
       </c>
-      <c r="E21" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -847,9 +779,6 @@
       <c r="D22" s="3" t="n">
         <v/>
       </c>
-      <c r="E22" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -864,9 +793,6 @@
       <c r="D23" s="3" t="n">
         <v/>
       </c>
-      <c r="E23" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -881,9 +807,6 @@
       <c r="D24" s="3" t="n">
         <v/>
       </c>
-      <c r="E24" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -898,9 +821,6 @@
       <c r="D25" s="3" t="n">
         <v/>
       </c>
-      <c r="E25" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -915,9 +835,6 @@
       <c r="D26" s="3" t="n">
         <v/>
       </c>
-      <c r="E26" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -932,9 +849,6 @@
       <c r="D27" s="3" t="n">
         <v/>
       </c>
-      <c r="E27" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -949,9 +863,6 @@
       <c r="D28" s="3" t="n">
         <v/>
       </c>
-      <c r="E28" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -966,9 +877,6 @@
       <c r="D29" s="3" t="n">
         <v/>
       </c>
-      <c r="E29" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -983,9 +891,6 @@
       <c r="D30" s="3" t="n">
         <v/>
       </c>
-      <c r="E30" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1000,9 +905,6 @@
       <c r="D31" s="3" t="n">
         <v/>
       </c>
-      <c r="E31" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1017,9 +919,6 @@
       <c r="D32" s="3" t="n">
         <v/>
       </c>
-      <c r="E32" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1034,9 +933,6 @@
       <c r="D33" s="3" t="n">
         <v/>
       </c>
-      <c r="E33" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1051,9 +947,6 @@
       <c r="D34" s="3" t="n">
         <v/>
       </c>
-      <c r="E34" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1068,9 +961,6 @@
       <c r="D35" s="3" t="n">
         <v/>
       </c>
-      <c r="E35" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1085,9 +975,6 @@
       <c r="D36" s="3" t="n">
         <v/>
       </c>
-      <c r="E36" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1102,9 +989,6 @@
       <c r="D37" s="3" t="n">
         <v/>
       </c>
-      <c r="E37" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1119,9 +1003,6 @@
       <c r="D38" s="3" t="n">
         <v/>
       </c>
-      <c r="E38" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1136,9 +1017,6 @@
       <c r="D39" s="3" t="n">
         <v/>
       </c>
-      <c r="E39" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1153,9 +1031,6 @@
       <c r="D40" s="3" t="n">
         <v/>
       </c>
-      <c r="E40" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1170,9 +1045,6 @@
       <c r="D41" s="3" t="n">
         <v/>
       </c>
-      <c r="E41" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1187,9 +1059,6 @@
       <c r="D42" s="3" t="n">
         <v/>
       </c>
-      <c r="E42" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1204,9 +1073,6 @@
       <c r="D43" s="3" t="n">
         <v/>
       </c>
-      <c r="E43" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1221,9 +1087,6 @@
       <c r="D44" s="3" t="n">
         <v/>
       </c>
-      <c r="E44" s="3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1233,13 +1096,10 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1244.621309450054</v>
+        <v>1139.072</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>1244.621309450054</v>
+        <v>1139.072</v>
       </c>
     </row>
     <row r="46">
@@ -1250,13 +1110,10 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1284.057808495028</v>
+        <v>1146.504</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1284.057808495028</v>
+        <v>1146.504</v>
       </c>
     </row>
     <row r="47">
@@ -1267,13 +1124,10 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1324.743874332017</v>
+        <v>1184.662</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>1324.743874332017</v>
+        <v>1184.662</v>
       </c>
     </row>
     <row r="48">
@@ -1284,13 +1138,10 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1366.719100160356</v>
+        <v>1229.948</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>1366.719100160356</v>
+        <v>1229.948</v>
       </c>
     </row>
     <row r="49">
@@ -1301,13 +1152,10 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1410.024333711304</v>
+        <v>1306.013</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>1410.024333711304</v>
+        <v>1306.013</v>
       </c>
     </row>
     <row r="50">
@@ -1318,13 +1166,10 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1454.701716998567</v>
+        <v>1351.434</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>1454.701716998567</v>
+        <v>1351.434</v>
       </c>
     </row>
     <row r="51">
@@ -1335,13 +1180,10 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1500.794727328338</v>
+        <v>1396.587</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>1500.794727328338</v>
+        <v>1396.587</v>
       </c>
     </row>
     <row r="52">
@@ -1352,13 +1194,10 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1548.348219608763</v>
+        <v>1476.643</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1548.348219608763</v>
+        <v>1476.643</v>
       </c>
     </row>
     <row r="53">
@@ -1369,13 +1208,10 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1597.408469999999</v>
+        <v>1365.253</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1597.408469999999</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v/>
+        <v>1365.253</v>
       </c>
     </row>
     <row r="54">
@@ -1386,13 +1222,10 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1685.925941106754</v>
+        <v>1440.905999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1685.925941106754</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v/>
+        <v>1440.905999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1403,13 +1236,10 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1796.951582301683</v>
+        <v>1535.796</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1796.951582301683</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v/>
+        <v>1535.796</v>
       </c>
     </row>
     <row r="56">
@@ -1420,13 +1250,10 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1788.624366700626</v>
+        <v>1528.679</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1788.624366700626</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v/>
+        <v>1528.679</v>
       </c>
     </row>
     <row r="57">
@@ -1437,13 +1264,10 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1744.703189346055</v>
+        <v>1491.141</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1744.703189346055</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v/>
+        <v>1491.141</v>
       </c>
     </row>
     <row r="58">
@@ -1454,13 +1278,10 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1758.556531023239</v>
+        <v>1502.981</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1758.556531023239</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v/>
+        <v>1502.981</v>
       </c>
     </row>
     <row r="59">
@@ -1471,13 +1292,10 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1840.488984650332</v>
+        <v>1573.006</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1840.488984650332</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v/>
+        <v>1573.006</v>
       </c>
     </row>
     <row r="60">
@@ -1488,13 +1306,10 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1918.846948511902</v>
+        <v>1639.976</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1918.846948511902</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v/>
+        <v>1639.976</v>
       </c>
     </row>
     <row r="61">
@@ -1505,13 +1320,10 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2019.549276056679</v>
+        <v>1726.043</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>2019.549276056679</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v/>
+        <v>1726.043</v>
       </c>
     </row>
     <row r="62">
@@ -1522,13 +1334,10 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2095.189223641552</v>
+        <v>1790.69</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2095.189223641552</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v/>
+        <v>1790.69</v>
       </c>
     </row>
     <row r="63">
@@ -1539,13 +1348,10 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>2090.011771198855</v>
+        <v>1786.265</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2090.011771198855</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v/>
+        <v>1786.265</v>
       </c>
     </row>
     <row r="64">
@@ -1556,13 +1362,10 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1874.303306818457</v>
+        <v>1601.906</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1874.303306818457</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v/>
+        <v>1601.906</v>
       </c>
     </row>
     <row r="65">
@@ -1573,13 +1376,10 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1869.138724879007</v>
+        <v>1597.491999999999</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1869.138724879007</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v/>
+        <v>1597.491999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1590,13 +1390,10 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1947.08717272816</v>
+        <v>1664.111999999999</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1947.08717272816</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v/>
+        <v>1664.111999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1607,13 +1404,10 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2043.129208051635</v>
+        <v>1746.195999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2043.129208051635</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v/>
+        <v>1746.195999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1624,13 +1418,10 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2103.736407843564</v>
+        <v>1797.995</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2103.736407843564</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v/>
+        <v>1797.995</v>
       </c>
     </row>
     <row r="69">
@@ -1641,13 +1432,10 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2220.304555755116</v>
+        <v>1897.622</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2220.304555755116</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v/>
+        <v>1897.622</v>
       </c>
     </row>
     <row r="70">
@@ -1658,13 +1446,10 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2318.601269238382</v>
+        <v>1981.633</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2318.601269238382</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v/>
+        <v>1981.633</v>
       </c>
     </row>
     <row r="71">
@@ -1675,13 +1460,10 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2359.39257421234</v>
+        <v>2016.496</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2359.39257421234</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v/>
+        <v>2016.496</v>
       </c>
     </row>
     <row r="72">
@@ -1692,13 +1474,10 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2474.870239485114</v>
+        <v>2115.191</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2474.870239485114</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v/>
+        <v>2115.191</v>
       </c>
     </row>
     <row r="73">
@@ -1709,13 +1488,10 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2617.765586812063</v>
+        <v>2237.319</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2617.765586812063</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v/>
+        <v>2237.319</v>
       </c>
     </row>
     <row r="74">
@@ -1726,13 +1502,10 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2739.832949747497</v>
+        <v>2341.646</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2739.832949747497</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v/>
+        <v>2341.646</v>
       </c>
     </row>
     <row r="75">
@@ -1743,13 +1516,10 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2710.340776578992</v>
+        <v>2316.44</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2710.340776578992</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v/>
+        <v>2316.44</v>
       </c>
     </row>
     <row r="76">
@@ -1760,13 +1530,10 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2887.166280603295</v>
+        <v>2467.567</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2887.166280603295</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v/>
+        <v>2467.567</v>
       </c>
     </row>
     <row r="77">
@@ -1777,13 +1544,10 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>3127.08065145477</v>
+        <v>2672.614</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>3127.08065145477</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v/>
+        <v>2672.614</v>
       </c>
     </row>
     <row r="78">
@@ -1794,13 +1558,10 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>3302.856624441536</v>
+        <v>2822.844</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>3302.856624441536</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v/>
+        <v>2822.844</v>
       </c>
     </row>
     <row r="79">
@@ -1811,13 +1572,10 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>3482.18017614158</v>
+        <v>2976.106</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>3482.18017614158</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v/>
+        <v>2976.106</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2039,44 +1797,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>S504-INTERP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DPR (markdown)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DPR (markdown)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t># S504 — Variable Capital (V*)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t># S504 — Variable Capital (V*)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
+          <t>**Source Table**: Appendix H.1</t>
         </is>
       </c>
     </row>
@@ -2084,7 +1838,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix H.1</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
@@ -2092,7 +1846,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Units**: billions_usd</t>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
         </is>
       </c>
     </row>
@@ -2100,7 +1854,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
@@ -2108,87 +1862,87 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Variable Capital: wages of productive labor under S&amp;T's classification. Drives the rate of exploitation S506 and feeds extension formulas.</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>## Subseries</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>| Subseries | Source | Period | Units |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
@@ -2196,7 +1950,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| `S504-A` | S&amp;T 1994 Appendix H.1 | 1948-1989 | billions_dollars |</t>
         </is>
       </c>
     </row>
@@ -2204,7 +1958,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>| `S504-A` | S&amp;T 1994 Appendix H.1 | 1948-1989 | billions_dollars |</t>
+          <t>| `S504-EXT` | BEA NIPA + BLS CES (derived V* = (V*/W)·W) | 1998-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
@@ -2212,7 +1966,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>| `S504-EXT` | BEA NIPA + BLS CES (derived V* = (V*/W)·W) | 1998-2024 | billions_dollars |</t>
+          <t>| `S504-INTERP` | Log-linear interp between S504-A(1989) and S504-EXT(1998) | 1990-1997 | billions_dollars |</t>
         </is>
       </c>
     </row>
@@ -2220,63 +1974,63 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>| `S504-INTERP` | Log-linear interp between S504-A(1989) and S504-EXT(1998) | 1990-1997 | billions_dollars |</t>
+          <t>| `S504-COMBINED` | S504-A ∪ S504-INTERP ∪ S504-EXT | 1948-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>| `S504-COMBINED` | S504-A ∪ S504-INTERP ∪ S504-EXT | 1948-2024 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>### S504-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>### S504-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+          <t>2. Extract column `V_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
@@ -2284,51 +2038,51 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2. Extract column `V_star` (and the `year` index).</t>
+          <t>3. No further transformation — this is the canonical published value.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>### S504-INTERP (1990-1997 bridge)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>### S504-INTERP (1990-1997 bridge)</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>**1990-1997 bridge**: log-linear interpolation between the book 1989 endpoint</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>**1990-1997 bridge**: log-linear interpolation between the book 1989 endpoint</t>
+          <t>(`S504-A[1989]` = 1206.40 $B) and the BEA-derived first-EXT value</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2090,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(`S504-A[1989]` = 1206.40 $B) and the BEA-derived first-EXT value</t>
+          <t>(`S504-EXT[1998]` = 1620.23 $B), consistent with the S501–S503 bridge per</t>
         </is>
       </c>
     </row>
@@ -2344,39 +2098,39 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(`S504-EXT[1998]` = 1620.23 $B), consistent with the S501–S503 bridge per</t>
+          <t>`Technical/Build/BUILD_NARRATIVE.md` Stage 5 cohort 3.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>`Technical/Build/BUILD_NARRATIVE.md` Stage 5 cohort 3.</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Formula: `v(t) = exp( ln(v0) + (t - 1989)/(1998 - 1989) · (ln(v1) - ln(v0)) )`</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Formula: `v(t) = exp( ln(v0) + (t - 1989)/(1998 - 1989) · (ln(v1) - ln(v0)) )`</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>These eight values are **INTERPOLATED estimates**, not published BEA data.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>These eight values are **INTERPOLATED estimates**, not published BEA data.</t>
+          <t>Documentation script: `code/M04_manual/M04_S504_1990_1997_bridge.py`</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2138,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Documentation script: `code/M04_manual/M04_S504_1990_1997_bridge.py`</t>
+          <t>(also acts as a verifier — re-derives values from endpoints and asserts</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2146,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(also acts as a verifier — re-derives values from endpoints and asserts</t>
+          <t>equality with the on-disk S504-INTERP rows). Sample values: 1991 = 1288.12,</t>
         </is>
       </c>
     </row>
@@ -2400,39 +2154,39 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>equality with the on-disk S504-INTERP rows). Sample values: 1991 = 1288.12,</t>
+          <t>1995 = 1468.52.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1995 = 1468.52.</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>### S504-EXT (1998-2024)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>### S504-EXT (1998-2024)</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Derived V* = (V*/W) · W where V*/W comes from `S504-EXT` (S512 must run</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Derived V* = (V*/W) · W where V*/W comes from `S504-EXT` (S512 must run</t>
+          <t>first) and W is BEA NIPA T20100 total compensation. Begins 1998 because</t>
         </is>
       </c>
     </row>
@@ -2440,143 +2194,143 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>first) and W is BEA NIPA T20100 total compensation. Begins 1998 because</t>
+          <t>BEA NIPA 6.2D (compensation by industry, NAICS) begins 1998.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>BEA NIPA 6.2D (compensation by industry, NAICS) begins 1998.</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>### S504-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>### S504-COMBINED</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Concatenation: 1948-1989 from S504-A, 1990-1997 from S504-INTERP (bridge),</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concatenation: 1948-1989 from S504-A, 1990-1997 from S504-INTERP (bridge),</t>
+          <t>1998-2024 from S504-EXT.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1998-2024 from S504-EXT.</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1948=88.41, 1972=324.30, 1989=1206.40</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
-        </is>
-      </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S504_variable_capital.py` writes to `data/intermediate/validation/S504.json`.</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>## Provenance Chain</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2338,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2346,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S504_variable_capital.py</t>
+          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2354,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S504.csv</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2362,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S504_variable_capital.py</t>
+          <t xml:space="preserve">                 └── data/final/S504.csv</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2370,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S504.csv</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
         </is>
       </c>
     </row>
@@ -2624,75 +2378,115 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S504_variable_capital.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>## Citations</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>**Cascade of the S512 de-splice (DIV-A11/A12).** S504-EXT = de-spliced S512-EXT x T20100, now</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>real-data 1990-2024 (no log-linear bridge; S504-INTERP retired). V*_1998 = 1365.25 (was 1597.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>spliced). Registry formula typo queued for fix: V* = W x (V*/W), not W - (V*/W). V03 PASS 3/3.</t>
         </is>
       </c>
     </row>
@@ -3183,7 +2977,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
@@ -3243,7 +3037,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S512-EXT</t>
+          <t>S512-EXT, BEA_NIPA_T20100_total_compensation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3253,7 +3047,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>V* = W — (V*/W)</t>
+          <t>V* = (V*/W) x W</t>
         </is>
       </c>
     </row>
